--- a/data/raw/sales/Week 31/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 31/Audio_Array/other_channels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 31\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA523158-38DC-423C-8F86-68B109510E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E836DC-3403-4276-8E92-B04E8894FF49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="162">
   <si>
     <t>SKU</t>
   </si>
@@ -239,13 +239,301 @@
   </si>
   <si>
     <t>ARETE ELEMENTS</t>
+  </si>
+  <si>
+    <t>AI-04 Red</t>
+  </si>
+  <si>
+    <t>FBA76863</t>
+  </si>
+  <si>
+    <t>AI-03</t>
+  </si>
+  <si>
+    <t>FBA79106</t>
+  </si>
+  <si>
+    <t>AM-C44</t>
+  </si>
+  <si>
+    <t>FBA79010</t>
+  </si>
+  <si>
+    <t>AM-C42</t>
+  </si>
+  <si>
+    <t>FBA79445</t>
+  </si>
+  <si>
+    <t>AM-W32</t>
+  </si>
+  <si>
+    <t>FBA75690</t>
+  </si>
+  <si>
+    <t>AM-C10</t>
+  </si>
+  <si>
+    <t>FBA75677</t>
+  </si>
+  <si>
+    <t>AM-C5</t>
+  </si>
+  <si>
+    <t>FBA79444</t>
+  </si>
+  <si>
+    <t>AM-W20</t>
+  </si>
+  <si>
+    <t>FBA79064</t>
+  </si>
+  <si>
+    <t>AA-25</t>
+  </si>
+  <si>
+    <t>FBA76730</t>
+  </si>
+  <si>
+    <t>AM-C27</t>
+  </si>
+  <si>
+    <t>FBA77171</t>
+  </si>
+  <si>
+    <t>AC-6XL</t>
+  </si>
+  <si>
+    <t>FBA78925</t>
+  </si>
+  <si>
+    <t>AM-C11X</t>
+  </si>
+  <si>
+    <t>FBA79011</t>
+  </si>
+  <si>
+    <t>AM-C43</t>
+  </si>
+  <si>
+    <t>FBA79009</t>
+  </si>
+  <si>
+    <t>AM-C41</t>
+  </si>
+  <si>
+    <t>FBA76862</t>
+  </si>
+  <si>
+    <t>AM-C28</t>
+  </si>
+  <si>
+    <t>FBA79356</t>
+  </si>
+  <si>
+    <t>AA-19WL</t>
+  </si>
+  <si>
+    <t>FBA75674</t>
+  </si>
+  <si>
+    <t>AM-C2</t>
+  </si>
+  <si>
+    <t>FBA78960</t>
+  </si>
+  <si>
+    <t>AM-C39</t>
+  </si>
+  <si>
+    <t>FBA79104</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t>FBA79008</t>
+  </si>
+  <si>
+    <t>AI-06</t>
+  </si>
+  <si>
+    <t>FBA75691</t>
+  </si>
+  <si>
+    <t>AM-W14</t>
+  </si>
+  <si>
+    <t>FBA79449</t>
+  </si>
+  <si>
+    <t>AM-W36</t>
+  </si>
+  <si>
+    <t>FBA75679</t>
+  </si>
+  <si>
+    <t>AA-02</t>
+  </si>
+  <si>
+    <t>FBA75680</t>
+  </si>
+  <si>
+    <t>AM-C6</t>
+  </si>
+  <si>
+    <t>FBA78973</t>
+  </si>
+  <si>
+    <t>AA-19</t>
+  </si>
+  <si>
+    <t>FBA75676</t>
+  </si>
+  <si>
+    <t>AM-C4</t>
+  </si>
+  <si>
+    <t>FBA76414</t>
+  </si>
+  <si>
+    <t>AA-05</t>
+  </si>
+  <si>
+    <t>FBA79447</t>
+  </si>
+  <si>
+    <t>AM-W34</t>
+  </si>
+  <si>
+    <t>FBA78976</t>
+  </si>
+  <si>
+    <t>AA-22</t>
+  </si>
+  <si>
+    <t>FBA79103</t>
+  </si>
+  <si>
+    <t>AI-10</t>
+  </si>
+  <si>
+    <t>FBA79016</t>
+  </si>
+  <si>
+    <t>AM-C3a</t>
+  </si>
+  <si>
+    <t>FBA75683</t>
+  </si>
+  <si>
+    <t>AA-03</t>
+  </si>
+  <si>
+    <t>FBA79448</t>
+  </si>
+  <si>
+    <t>AM-W35</t>
+  </si>
+  <si>
+    <t>FBA76597</t>
+  </si>
+  <si>
+    <t>AA-06</t>
+  </si>
+  <si>
+    <t>FBA75675</t>
+  </si>
+  <si>
+    <t>AM-C3</t>
+  </si>
+  <si>
+    <t>FBA75678</t>
+  </si>
+  <si>
+    <t>AA-01</t>
+  </si>
+  <si>
+    <t>FBA78974</t>
+  </si>
+  <si>
+    <t>AA-20</t>
+  </si>
+  <si>
+    <t>FBA79105</t>
+  </si>
+  <si>
+    <t>AI-12</t>
+  </si>
+  <si>
+    <t>FBA78203</t>
+  </si>
+  <si>
+    <t>AM-C30</t>
+  </si>
+  <si>
+    <t>FBA75689</t>
+  </si>
+  <si>
+    <t>AM-W13</t>
+  </si>
+  <si>
+    <t>FBA75688</t>
+  </si>
+  <si>
+    <t>AM-W12</t>
+  </si>
+  <si>
+    <t>FBA79230</t>
+  </si>
+  <si>
+    <t>AM-W46</t>
+  </si>
+  <si>
+    <t>FBA78204</t>
+  </si>
+  <si>
+    <t>AM-C31</t>
+  </si>
+  <si>
+    <t>FBA78975</t>
+  </si>
+  <si>
+    <t>AA-21</t>
+  </si>
+  <si>
+    <t>FBA78424</t>
+  </si>
+  <si>
+    <t>AM-C37</t>
+  </si>
+  <si>
+    <t>FBA75681</t>
+  </si>
+  <si>
+    <t>AM-C7</t>
+  </si>
+  <si>
+    <t>FBA78961</t>
+  </si>
+  <si>
+    <t>AM-C40</t>
+  </si>
+  <si>
+    <t>FBA75692</t>
+  </si>
+  <si>
+    <t>AM-C11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +580,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -319,7 +612,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -342,11 +635,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -391,6 +699,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2711,7 +3029,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E3AF619-DC76-4D87-9D69-4310FD74DCA6}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -2737,6 +3055,975 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="18">
+        <v>12</v>
+      </c>
+      <c r="D2" s="19">
+        <v>27896.610169491527</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="18">
+        <v>4</v>
+      </c>
+      <c r="D3" s="19">
+        <v>17050</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="18">
+        <v>2</v>
+      </c>
+      <c r="D4" s="19">
+        <v>6826.2711864406783</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="18">
+        <v>1</v>
+      </c>
+      <c r="D5" s="19">
+        <v>4014.406779661017</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="18">
+        <v>2</v>
+      </c>
+      <c r="D6" s="19">
+        <v>3742.3728813559323</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="18">
+        <v>1</v>
+      </c>
+      <c r="D7" s="19">
+        <v>3394.0677966101698</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="18">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19">
+        <v>3388.9830508474579</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19">
+        <v>2146.6101694915255</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="18">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
+        <v>1659.3220338983051</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="18">
+        <v>2</v>
+      </c>
+      <c r="D11" s="19">
+        <v>1476.2711864406781</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="18">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19">
+        <v>1055.9322033898306</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="18">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19">
+        <v>439.83050847457628</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="18">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19">
+        <v>0</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="18">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19">
+        <v>0</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="18">
+        <v>0</v>
+      </c>
+      <c r="D16" s="19">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="18">
+        <v>0</v>
+      </c>
+      <c r="D17" s="19">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="18">
+        <v>0</v>
+      </c>
+      <c r="D18" s="19">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="18">
+        <v>0</v>
+      </c>
+      <c r="D19" s="19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="18">
+        <v>0</v>
+      </c>
+      <c r="D20" s="19">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="18">
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="18">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="18">
+        <v>0</v>
+      </c>
+      <c r="D23" s="19">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="18">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="18">
+        <v>0</v>
+      </c>
+      <c r="D25" s="19">
+        <v>0</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="18">
+        <v>0</v>
+      </c>
+      <c r="D26" s="19">
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="18">
+        <v>0</v>
+      </c>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="18">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19">
+        <v>0</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="18">
+        <v>0</v>
+      </c>
+      <c r="D30" s="19">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="18">
+        <v>0</v>
+      </c>
+      <c r="D31" s="19">
+        <v>0</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="18">
+        <v>0</v>
+      </c>
+      <c r="D32" s="19">
+        <v>0</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="18">
+        <v>0</v>
+      </c>
+      <c r="D33" s="19">
+        <v>0</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="18">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="18">
+        <v>0</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="18">
+        <v>0</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="18">
+        <v>0</v>
+      </c>
+      <c r="D37" s="19">
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="18">
+        <v>0</v>
+      </c>
+      <c r="D38" s="19">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="18">
+        <v>0</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="18">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="18">
+        <v>0</v>
+      </c>
+      <c r="D41" s="19">
+        <v>0</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="18">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19">
+        <v>0</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="18">
+        <v>0</v>
+      </c>
+      <c r="D43" s="19">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="18">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19">
+        <v>0</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="18">
+        <v>0</v>
+      </c>
+      <c r="D45" s="19">
+        <v>0</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="18">
+        <v>0</v>
+      </c>
+      <c r="D46" s="19">
+        <v>0</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="18">
+        <v>0</v>
+      </c>
+      <c r="D47" s="19">
+        <v>0</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="18">
+        <v>0</v>
+      </c>
+      <c r="D48" s="19">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="18">
+        <v>0</v>
+      </c>
+      <c r="D49" s="19">
+        <v>0</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C50" s="18">
+        <v>0</v>
+      </c>
+      <c r="D50" s="19">
+        <v>0</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="18">
+        <v>0</v>
+      </c>
+      <c r="D51" s="19">
+        <v>0</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="18">
+        <v>0</v>
+      </c>
+      <c r="D52" s="19">
+        <v>0</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C53" s="18">
+        <v>0</v>
+      </c>
+      <c r="D53" s="19">
+        <v>0</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="18">
+        <v>0</v>
+      </c>
+      <c r="D54" s="19">
+        <v>0</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55" s="18">
+        <v>0</v>
+      </c>
+      <c r="D55" s="19">
+        <v>0</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="18">
+        <v>0</v>
+      </c>
+      <c r="D56" s="19">
+        <v>0</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="18">
+        <v>0</v>
+      </c>
+      <c r="D57" s="19">
+        <v>0</v>
+      </c>
+      <c r="E57" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C58" s="18">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19">
+        <v>0</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
